--- a/projects/hq-ssc-equipment-rooms/HQ_SSC_equipment_rooms.xlsx
+++ b/projects/hq-ssc-equipment-rooms/HQ_SSC_equipment_rooms.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Equipment and rooms'!$A$1:$K$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Equipment and rooms'!$A$1:$K$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>CCU_B0003A</t>
+          <t>CCU-B-0003A</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -2629,9 +2629,21 @@
           <t>B1.106 VVIP PARKING 6 CAR SPOTS</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Chauffer Room B.117</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Basment Floor/BF-2</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
           <t>YES</t>
@@ -2639,144 +2651,120 @@
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>a CRAC is a computer-room unit and the ontology puts it in a parking bay</t>
+          <t>the BMS screen puts it in Chauffer Room B.117 and the ontology in B1.106 VVIP PARKING 6 CAR SPOTS; the dot is in the Chauffer Room band, one wall north of VIP Parking B.106</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>HQ</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>CCU_B0003B</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>brick:CRAC</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_CCU_B0003B</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_B1_106_VVIP_PARKING_6_CAR_SPOTS</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>B1.106 VVIP PARKING 6 CAR SPOTS</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr"/>
-      <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr"/>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K46" s="8" t="inlineStr">
-        <is>
-          <t>a CRAC is a computer-room unit and the ontology puts it in a parking bay</t>
-        </is>
-      </c>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>HQ</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>CCU_B0004A</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>brick:CRAC</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_CCU_B0004A</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_B1_106_VVIP_PARKING_6_CAR_SPOTS</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>B1.106 VVIP PARKING 6 CAR SPOTS</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr"/>
-      <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K47" s="8" t="inlineStr">
-        <is>
-          <t>a CRAC is a computer-room unit and the ontology puts it in a parking bay</t>
-        </is>
-      </c>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>HQ</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>CCU_B0004B</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>brick:CRAC</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_CCU_B0004B</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_B1_106_VVIP_PARKING_6_CAR_SPOTS</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>B1.106 VVIP PARKING 6 CAR SPOTS</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr"/>
-      <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr"/>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K48" s="8" t="inlineStr">
-        <is>
-          <t>a CRAC is a computer-room unit and the ontology puts it in a parking bay</t>
-        </is>
-      </c>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -2786,7 +2774,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>CCU_B0005</t>
+          <t>CCU-B-0005</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -2805,9 +2793,21 @@
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
-      <c r="G49" s="7" t="inlineStr"/>
-      <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>VIP Parking B.115</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Basment Floor/BF-2</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
           <t>YES</t>
@@ -2815,189 +2815,205 @@
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the BMS screen puts it in VIP Parking B.115 and the ontology in entity:&lt;Location&gt;; and the screen reading was itself marked as wanting a second look when it was made; four leaders converge on one dot inside VIP Parking B.115, so the room is certain and which of the four walked it is not</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>HQ</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>CCU_B0006</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>CCU-B-0006</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>brick:CRAC</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_CCU_B0006</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_B1_115_VVIP_PARKING_4_CAR_SPOTS</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>B1.115 VVIP PARKING 4 CAR SPOTS</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr"/>
-      <c r="H50" s="7" t="inlineStr"/>
-      <c r="I50" s="7" t="inlineStr"/>
-      <c r="J50" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K50" s="8" t="inlineStr">
-        <is>
-          <t>a CRAC is a computer-room unit and the ontology puts it in a parking bay</t>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>VIP Parking B.115</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>HQ/Basment Floor/BF-2</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr"/>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>four leaders converge on one dot inside VIP Parking B.115</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>HQ</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>CCU_B0007</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>CCU-B-0007</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>brick:CRAC</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_CCU_B0007</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_B1_115_VVIP_PARKING_4_CAR_SPOTS</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>B1.115 VVIP PARKING 4 CAR SPOTS</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K51" s="8" t="inlineStr">
-        <is>
-          <t>a CRAC is a computer-room unit and the ontology puts it in a parking bay</t>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>VIP Parking B.115</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>HQ/Basment Floor/BF-2</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>four leaders converge on one dot inside VIP Parking B.115</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>HQ</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>CCU_B0008</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>CCU-B-0008</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>brick:CRAC</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_CCU_B0008</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_B1_115_VVIP_PARKING_4_CAR_SPOTS</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>B1.115 VVIP PARKING 4 CAR SPOTS</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr"/>
-      <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr"/>
-      <c r="J52" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K52" s="8" t="inlineStr">
-        <is>
-          <t>a CRAC is a computer-room unit and the ontology puts it in a parking bay</t>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>VIP Parking B.115</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>HQ/Basment Floor/BF-2</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>four leaders converge on one dot inside VIP Parking B.115</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>HQ</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>CCU_B0009</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>brick:CRAC</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_CCU_B0009</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>entity:HQ_B1_115_VVIP_PARKING_4_CAR_SPOTS</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>B1.115 VVIP PARKING 4 CAR SPOTS</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr"/>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K53" s="8" t="inlineStr">
-        <is>
-          <t>a CRAC is a computer-room unit and the ontology puts it in a parking bay</t>
-        </is>
-      </c>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="5" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -3437,7 +3453,11 @@
       </c>
       <c r="F64" s="7" t="inlineStr"/>
       <c r="G64" s="7" t="inlineStr"/>
-      <c r="H64" s="7" t="inlineStr"/>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-3</t>
+        </is>
+      </c>
       <c r="I64" s="7" t="inlineStr"/>
       <c r="J64" s="7" t="inlineStr">
         <is>
@@ -3446,7 +3466,7 @@
       </c>
       <c r="K64" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3498,11 @@
       </c>
       <c r="F65" s="7" t="inlineStr"/>
       <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-3</t>
+        </is>
+      </c>
       <c r="I65" s="7" t="inlineStr"/>
       <c r="J65" s="7" t="inlineStr">
         <is>
@@ -3487,7 +3511,7 @@
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3543,11 @@
       </c>
       <c r="F66" s="7" t="inlineStr"/>
       <c r="G66" s="7" t="inlineStr"/>
-      <c r="H66" s="7" t="inlineStr"/>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-3</t>
+        </is>
+      </c>
       <c r="I66" s="7" t="inlineStr"/>
       <c r="J66" s="7" t="inlineStr">
         <is>
@@ -3528,7 +3556,7 @@
       </c>
       <c r="K66" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3588,11 @@
       </c>
       <c r="F67" s="7" t="inlineStr"/>
       <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr"/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-3</t>
+        </is>
+      </c>
       <c r="I67" s="7" t="inlineStr"/>
       <c r="J67" s="7" t="inlineStr">
         <is>
@@ -3569,7 +3601,7 @@
       </c>
       <c r="K67" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3633,11 @@
       </c>
       <c r="F68" s="7" t="inlineStr"/>
       <c r="G68" s="7" t="inlineStr"/>
-      <c r="H68" s="7" t="inlineStr"/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-3</t>
+        </is>
+      </c>
       <c r="I68" s="7" t="inlineStr"/>
       <c r="J68" s="7" t="inlineStr">
         <is>
@@ -3610,7 +3646,7 @@
       </c>
       <c r="K68" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3678,11 @@
       </c>
       <c r="F69" s="7" t="inlineStr"/>
       <c r="G69" s="7" t="inlineStr"/>
-      <c r="H69" s="7" t="inlineStr"/>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-3</t>
+        </is>
+      </c>
       <c r="I69" s="7" t="inlineStr"/>
       <c r="J69" s="7" t="inlineStr">
         <is>
@@ -3651,7 +3691,7 @@
       </c>
       <c r="K69" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3723,11 @@
       </c>
       <c r="F70" s="7" t="inlineStr"/>
       <c r="G70" s="7" t="inlineStr"/>
-      <c r="H70" s="7" t="inlineStr"/>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-3</t>
+        </is>
+      </c>
       <c r="I70" s="7" t="inlineStr"/>
       <c r="J70" s="7" t="inlineStr">
         <is>
@@ -3692,7 +3736,7 @@
       </c>
       <c r="K70" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3768,11 @@
       </c>
       <c r="F71" s="7" t="inlineStr"/>
       <c r="G71" s="7" t="inlineStr"/>
-      <c r="H71" s="7" t="inlineStr"/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-4</t>
+        </is>
+      </c>
       <c r="I71" s="7" t="inlineStr"/>
       <c r="J71" s="7" t="inlineStr">
         <is>
@@ -3733,7 +3781,7 @@
       </c>
       <c r="K71" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3895,11 @@
       </c>
       <c r="F74" s="7" t="inlineStr"/>
       <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="7" t="inlineStr"/>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-4</t>
+        </is>
+      </c>
       <c r="I74" s="7" t="inlineStr"/>
       <c r="J74" s="7" t="inlineStr">
         <is>
@@ -3856,7 +3908,7 @@
       </c>
       <c r="K74" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3940,11 @@
       </c>
       <c r="F75" s="7" t="inlineStr"/>
       <c r="G75" s="7" t="inlineStr"/>
-      <c r="H75" s="7" t="inlineStr"/>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-4</t>
+        </is>
+      </c>
       <c r="I75" s="7" t="inlineStr"/>
       <c r="J75" s="7" t="inlineStr">
         <is>
@@ -3897,7 +3953,7 @@
       </c>
       <c r="K75" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3985,11 @@
       </c>
       <c r="F76" s="7" t="inlineStr"/>
       <c r="G76" s="7" t="inlineStr"/>
-      <c r="H76" s="7" t="inlineStr"/>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-4</t>
+        </is>
+      </c>
       <c r="I76" s="7" t="inlineStr"/>
       <c r="J76" s="7" t="inlineStr">
         <is>
@@ -3938,7 +3998,7 @@
       </c>
       <c r="K76" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -3970,7 +4030,11 @@
       </c>
       <c r="F77" s="7" t="inlineStr"/>
       <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-4</t>
+        </is>
+      </c>
       <c r="I77" s="7" t="inlineStr"/>
       <c r="J77" s="7" t="inlineStr">
         <is>
@@ -3979,7 +4043,7 @@
       </c>
       <c r="K77" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4075,11 @@
       </c>
       <c r="F78" s="7" t="inlineStr"/>
       <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr"/>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-4</t>
+        </is>
+      </c>
       <c r="I78" s="7" t="inlineStr"/>
       <c r="J78" s="7" t="inlineStr">
         <is>
@@ -4020,7 +4088,7 @@
       </c>
       <c r="K78" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4120,11 @@
       </c>
       <c r="F79" s="7" t="inlineStr"/>
       <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-4</t>
+        </is>
+      </c>
       <c r="I79" s="7" t="inlineStr"/>
       <c r="J79" s="7" t="inlineStr">
         <is>
@@ -4061,7 +4133,7 @@
       </c>
       <c r="K79" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4093,7 +4165,11 @@
       </c>
       <c r="F80" s="7" t="inlineStr"/>
       <c r="G80" s="7" t="inlineStr"/>
-      <c r="H80" s="7" t="inlineStr"/>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-4</t>
+        </is>
+      </c>
       <c r="I80" s="7" t="inlineStr"/>
       <c r="J80" s="7" t="inlineStr">
         <is>
@@ -4102,7 +4178,7 @@
       </c>
       <c r="K80" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4210,11 @@
       </c>
       <c r="F81" s="7" t="inlineStr"/>
       <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-4</t>
+        </is>
+      </c>
       <c r="I81" s="7" t="inlineStr"/>
       <c r="J81" s="7" t="inlineStr">
         <is>
@@ -4143,7 +4223,7 @@
       </c>
       <c r="K81" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4255,11 @@
       </c>
       <c r="F82" s="7" t="inlineStr"/>
       <c r="G82" s="7" t="inlineStr"/>
-      <c r="H82" s="7" t="inlineStr"/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-4</t>
+        </is>
+      </c>
       <c r="I82" s="7" t="inlineStr"/>
       <c r="J82" s="7" t="inlineStr">
         <is>
@@ -4184,7 +4268,7 @@
       </c>
       <c r="K82" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4300,11 @@
       </c>
       <c r="F83" s="7" t="inlineStr"/>
       <c r="G83" s="7" t="inlineStr"/>
-      <c r="H83" s="7" t="inlineStr"/>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
       <c r="I83" s="7" t="inlineStr"/>
       <c r="J83" s="7" t="inlineStr">
         <is>
@@ -4225,7 +4313,7 @@
       </c>
       <c r="K83" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4345,11 @@
       </c>
       <c r="F84" s="7" t="inlineStr"/>
       <c r="G84" s="7" t="inlineStr"/>
-      <c r="H84" s="7" t="inlineStr"/>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
       <c r="I84" s="7" t="inlineStr"/>
       <c r="J84" s="7" t="inlineStr">
         <is>
@@ -4266,7 +4358,7 @@
       </c>
       <c r="K84" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4390,11 @@
       </c>
       <c r="F85" s="7" t="inlineStr"/>
       <c r="G85" s="7" t="inlineStr"/>
-      <c r="H85" s="7" t="inlineStr"/>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
       <c r="I85" s="7" t="inlineStr"/>
       <c r="J85" s="7" t="inlineStr">
         <is>
@@ -4307,7 +4403,7 @@
       </c>
       <c r="K85" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4435,11 @@
       </c>
       <c r="F86" s="7" t="inlineStr"/>
       <c r="G86" s="7" t="inlineStr"/>
-      <c r="H86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
       <c r="I86" s="7" t="inlineStr"/>
       <c r="J86" s="7" t="inlineStr">
         <is>
@@ -4348,7 +4448,7 @@
       </c>
       <c r="K86" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4480,11 @@
       </c>
       <c r="F87" s="7" t="inlineStr"/>
       <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
       <c r="I87" s="7" t="inlineStr"/>
       <c r="J87" s="7" t="inlineStr">
         <is>
@@ -4389,7 +4493,7 @@
       </c>
       <c r="K87" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4525,11 @@
       </c>
       <c r="F88" s="7" t="inlineStr"/>
       <c r="G88" s="7" t="inlineStr"/>
-      <c r="H88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
       <c r="I88" s="7" t="inlineStr"/>
       <c r="J88" s="7" t="inlineStr">
         <is>
@@ -4430,7 +4538,7 @@
       </c>
       <c r="K88" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4570,11 @@
       </c>
       <c r="F89" s="7" t="inlineStr"/>
       <c r="G89" s="7" t="inlineStr"/>
-      <c r="H89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-1</t>
+        </is>
+      </c>
       <c r="I89" s="7" t="inlineStr"/>
       <c r="J89" s="7" t="inlineStr">
         <is>
@@ -4471,7 +4583,7 @@
       </c>
       <c r="K89" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4615,11 @@
       </c>
       <c r="F90" s="7" t="inlineStr"/>
       <c r="G90" s="7" t="inlineStr"/>
-      <c r="H90" s="7" t="inlineStr"/>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-1</t>
+        </is>
+      </c>
       <c r="I90" s="7" t="inlineStr"/>
       <c r="J90" s="7" t="inlineStr">
         <is>
@@ -4512,7 +4628,7 @@
       </c>
       <c r="K90" s="8" t="inlineStr">
         <is>
-          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room</t>
+          <t>the ontology points at the placeholder entity:&lt;Location&gt; rather than a room; the screen shows it on this car park deck, but the deck carries no room names at all - bay numbers, Exit and nothing else - so the placeholder cannot be resolved from it</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4640,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DX_B0001</t>
+          <t>DX-B-0001</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -4547,9 +4663,21 @@
           <t>B1.011 HV INTAKE</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr"/>
-      <c r="H91" s="5" t="inlineStr"/>
-      <c r="I91" s="5" t="inlineStr"/>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>HV Room B.011</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>HQ/Basment Floor/BF-1</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
       <c r="J91" s="5" t="inlineStr"/>
       <c r="K91" s="6" t="inlineStr"/>
     </row>
@@ -4591,41 +4719,61 @@
       <c r="K92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>HQ</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>DX_B0003</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>DX-B-0003</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>para:DXUnit</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>entity:HQ_DX_B0003</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>entity:HQ_B1_010_TRANSFORMER_SUBSTATION</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>B1.010 TRANSFORMER SUBSTATION</t>
         </is>
       </c>
-      <c r="G93" s="5" t="inlineStr"/>
-      <c r="H93" s="5" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr"/>
-      <c r="J93" s="5" t="inlineStr"/>
-      <c r="K93" s="6" t="inlineStr"/>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Unlabelled cell east of Transformer Substation B.010</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Basment Floor/BF-1</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K93" s="8" t="inlineStr">
+        <is>
+          <t>the dot is in a cell the screen does not name, so the ontology room cannot be confirmed from it; the BMS screen puts it in Unlabelled cell east of Transformer Substation B.010 and the ontology in B1.010 TRANSFORMER SUBSTATION; the top band of this plan is three cells and only the first two are named; the dot is in the third</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -4887,41 +5035,61 @@
       <c r="K100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>HQ</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>DX_B0011</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>DX-B-0011</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>para:DXUnit</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>entity:HQ_DX_B0011</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>entity:HQ_B1_009_MV_SWITCH_ROOM</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>B1.009 MV SWITCH ROOM</t>
         </is>
       </c>
-      <c r="G101" s="5" t="inlineStr"/>
-      <c r="H101" s="5" t="inlineStr"/>
-      <c r="I101" s="5" t="inlineStr"/>
-      <c r="J101" s="5" t="inlineStr"/>
-      <c r="K101" s="6" t="inlineStr"/>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>UPS Room B.26</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Basment Floor/BF-1</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K101" s="8" t="inlineStr">
+        <is>
+          <t>the BMS screen puts it in UPS Room B.26 and the ontology in B1.009 MV SWITCH ROOM</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -5072,41 +5240,61 @@
       <c r="K105" s="6" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>HQ</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>DX_B0016</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="inlineStr">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>DX-B-0016</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
         <is>
           <t>para:DXUnit</t>
         </is>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t>entity:HQ_DX_B0016</t>
         </is>
       </c>
-      <c r="E106" s="5" t="inlineStr">
+      <c r="E106" s="7" t="inlineStr">
         <is>
           <t>entity:HQ_B1_018_PA_ROOM</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr">
+      <c r="F106" s="7" t="inlineStr">
         <is>
           <t>B1.018 PA ROOM</t>
         </is>
       </c>
-      <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="5" t="inlineStr"/>
-      <c r="I106" s="5" t="inlineStr"/>
-      <c r="J106" s="5" t="inlineStr"/>
-      <c r="K106" s="6" t="inlineStr"/>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>AHU - 3 B.022</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Basment Floor/BF-2</t>
+        </is>
+      </c>
+      <c r="I106" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K106" s="8" t="inlineStr">
+        <is>
+          <t>the BMS screen puts it in AHU - 3 B.022 and the ontology in B1.018 PA ROOM</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
@@ -6113,8 +6301,746 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>JF-B-0001</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>Jet fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr"/>
+      <c r="E132" s="7" t="inlineStr"/>
+      <c r="F132" s="7" t="inlineStr"/>
+      <c r="G132" s="7" t="inlineStr"/>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-1</t>
+        </is>
+      </c>
+      <c r="I132" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J132" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K132" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>JF-B-0002</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>Jet fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr"/>
+      <c r="E133" s="7" t="inlineStr"/>
+      <c r="F133" s="7" t="inlineStr"/>
+      <c r="G133" s="7" t="inlineStr"/>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-1</t>
+        </is>
+      </c>
+      <c r="I133" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J133" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K133" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>JF-B-0003</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>Jet fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr"/>
+      <c r="E134" s="7" t="inlineStr"/>
+      <c r="F134" s="7" t="inlineStr"/>
+      <c r="G134" s="7" t="inlineStr"/>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-1</t>
+        </is>
+      </c>
+      <c r="I134" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J134" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K134" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>JF-B-0004</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>Jet fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr"/>
+      <c r="E135" s="7" t="inlineStr"/>
+      <c r="F135" s="7" t="inlineStr"/>
+      <c r="G135" s="7" t="inlineStr"/>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-1</t>
+        </is>
+      </c>
+      <c r="I135" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J135" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K135" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>JF-B-0005</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>Jet fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr"/>
+      <c r="E136" s="7" t="inlineStr"/>
+      <c r="F136" s="7" t="inlineStr"/>
+      <c r="G136" s="7" t="inlineStr"/>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-1</t>
+        </is>
+      </c>
+      <c r="I136" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J136" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K136" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>JF-B-0006</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>Jet fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr"/>
+      <c r="E137" s="7" t="inlineStr"/>
+      <c r="F137" s="7" t="inlineStr"/>
+      <c r="G137" s="7" t="inlineStr"/>
+      <c r="H137" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-1</t>
+        </is>
+      </c>
+      <c r="I137" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J137" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K137" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>JF-B-0007</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>Jet fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr"/>
+      <c r="E138" s="7" t="inlineStr"/>
+      <c r="F138" s="7" t="inlineStr"/>
+      <c r="G138" s="7" t="inlineStr"/>
+      <c r="H138" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
+      <c r="I138" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J138" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K138" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>JF-B-0008</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>Jet fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr"/>
+      <c r="E139" s="7" t="inlineStr"/>
+      <c r="F139" s="7" t="inlineStr"/>
+      <c r="G139" s="7" t="inlineStr"/>
+      <c r="H139" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
+      <c r="I139" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K139" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>JF-B-0009</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>Jet fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr"/>
+      <c r="E140" s="7" t="inlineStr"/>
+      <c r="F140" s="7" t="inlineStr"/>
+      <c r="G140" s="7" t="inlineStr"/>
+      <c r="H140" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
+      <c r="I140" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J140" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K140" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>JF-B-0010</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>Jet fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr"/>
+      <c r="E141" s="7" t="inlineStr"/>
+      <c r="F141" s="7" t="inlineStr"/>
+      <c r="G141" s="7" t="inlineStr"/>
+      <c r="H141" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
+      <c r="I141" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K141" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>IF-B-0001</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>Induction fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr"/>
+      <c r="E142" s="7" t="inlineStr"/>
+      <c r="F142" s="7" t="inlineStr"/>
+      <c r="G142" s="7" t="inlineStr"/>
+      <c r="H142" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-1</t>
+        </is>
+      </c>
+      <c r="I142" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J142" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K142" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>IF-B-0002</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t>Induction fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr"/>
+      <c r="E143" s="7" t="inlineStr"/>
+      <c r="F143" s="7" t="inlineStr"/>
+      <c r="G143" s="7" t="inlineStr"/>
+      <c r="H143" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-1</t>
+        </is>
+      </c>
+      <c r="I143" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J143" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K143" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>IF-B-0003</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>Induction fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr"/>
+      <c r="E144" s="7" t="inlineStr"/>
+      <c r="F144" s="7" t="inlineStr"/>
+      <c r="G144" s="7" t="inlineStr"/>
+      <c r="H144" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-1</t>
+        </is>
+      </c>
+      <c r="I144" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J144" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K144" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>IF-B-0004</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>Induction fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr"/>
+      <c r="E145" s="7" t="inlineStr"/>
+      <c r="F145" s="7" t="inlineStr"/>
+      <c r="G145" s="7" t="inlineStr"/>
+      <c r="H145" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
+      <c r="I145" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J145" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K145" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>IF-B-0005</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>Induction fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr"/>
+      <c r="E146" s="7" t="inlineStr"/>
+      <c r="F146" s="7" t="inlineStr"/>
+      <c r="G146" s="7" t="inlineStr"/>
+      <c r="H146" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
+      <c r="I146" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J146" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K146" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>IF-B-0006</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>Induction fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr"/>
+      <c r="E147" s="7" t="inlineStr"/>
+      <c r="F147" s="7" t="inlineStr"/>
+      <c r="G147" s="7" t="inlineStr"/>
+      <c r="H147" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
+      <c r="I147" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J147" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K147" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>IF-B-0007</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>Induction fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr"/>
+      <c r="E148" s="7" t="inlineStr"/>
+      <c r="F148" s="7" t="inlineStr"/>
+      <c r="G148" s="7" t="inlineStr"/>
+      <c r="H148" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
+      <c r="I148" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J148" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K148" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>IF-B-0008</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t>Induction fan (BMS screen only)</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr"/>
+      <c r="E149" s="7" t="inlineStr"/>
+      <c r="F149" s="7" t="inlineStr"/>
+      <c r="G149" s="7" t="inlineStr"/>
+      <c r="H149" s="7" t="inlineStr">
+        <is>
+          <t>HQ/Cark Park/CPF-2</t>
+        </is>
+      </c>
+      <c r="I149" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J149" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K149" s="8" t="inlineStr">
+        <is>
+          <t>this unit is drawn on the BMS screen and the ontology has no entity for it at all</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K131"/>
+  <autoFilter ref="A1:K149"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6125,7 +7051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6164,14 +7090,14 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>brick:CRAC</t>
+          <t>Induction fan (BMS screen only)</t>
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -6182,14 +7108,14 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>brick:Chilled_Water_Booster_Pump</t>
+          <t>Jet fan (BMS screen only)</t>
         </is>
       </c>
       <c r="C3" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -6200,14 +7126,14 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>brick:Heat_Exchanger</t>
+          <t>brick:CRAC</t>
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -6218,14 +7144,14 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>para:Car-Parking_Exhaust-Fan</t>
+          <t>brick:Chilled_Water_Booster_Pump</t>
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -6236,14 +7162,14 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>para:DXUnit</t>
+          <t>brick:Heat_Exchanger</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -6254,14 +7180,14 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>para:General_Exhaust-Fan</t>
+          <t>para:Car-Parking_Exhaust-Fan</t>
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -6272,14 +7198,14 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>para:Generator</t>
+          <t>para:DXUnit</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -6290,50 +7216,50 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>para:T_Exhaust-Fan</t>
+          <t>para:General_Exhaust-Fan</t>
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>SSC</t>
+          <t>HQ</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>brick:CRAC</t>
+          <t>para:Generator</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>SSC</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>brick:Chilled_Water_Booster_Pump</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>para:T_Exhaust-Fan</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="10" t="n">
-        <v>0</v>
+      <c r="D11" s="9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -6344,14 +7270,14 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>brick:Exhaust_Fan</t>
+          <t>brick:CRAC</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6362,11 +7288,11 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>brick:Heat_Exchanger</t>
+          <t>brick:Chilled_Water_Booster_Pump</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>0</v>
@@ -6380,14 +7306,14 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>para:DXUnit</t>
+          <t>brick:Exhaust_Fan</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -6398,13 +7324,49 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
+          <t>brick:Heat_Exchanger</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>SSC</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>para:DXUnit</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>SSC</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
           <t>para:Generator</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D17" s="10" t="n">
         <v>0</v>
       </c>
     </row>

--- a/projects/hq-ssc-equipment-rooms/HQ_SSC_equipment_rooms.xlsx
+++ b/projects/hq-ssc-equipment-rooms/HQ_SSC_equipment_rooms.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_038_SER-2</t>
+          <t>entity:SSC_B-038_Ser-2</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_038_SER-2</t>
+          <t>entity:SSC_B-038_Ser-2</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_038_SER-2</t>
+          <t>entity:SSC_B-038_Ser-2</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_038_SER-2</t>
+          <t>entity:SSC_B-038_Ser-2</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_038_SER-2</t>
+          <t>entity:SSC_B-038_Ser-2</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_038_SER-2</t>
+          <t>entity:SSC_B-038_Ser-2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_023_Q_TEL</t>
+          <t>entity:SSC_B-023_Q-Tel</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -967,61 +967,53 @@
       <c r="K8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>CCU-B-0004</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>brick:CRAC</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>entity:SSC_CCUB0004</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>entity:SSC_B1_023_Q_TEL</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>B1.023 QTEL</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>entity:SSC_B-017_MDF-2</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>B1.017 MDF-2</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>B.017 MDF-2</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>BF-part1</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>the BMS screen puts it in B.017 MDF-2 and the ontology in B1.023 QTEL</t>
-        </is>
-      </c>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1046,7 +1038,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_023_Q_TEL</t>
+          <t>entity:SSC_B-023_Q-Tel</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1083,7 +1075,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_023_Q_TEL</t>
+          <t>entity:SSC_B-023_Q-Tel</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1132,7 +1124,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_023_Q_TEL</t>
+          <t>entity:SSC_B-023_Q-Tel</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1181,7 +1173,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_023_Q_TEL</t>
+          <t>entity:SSC_B-023_Q-Tel</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1208,61 +1200,53 @@
       <c r="K13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>CCU-B-0007</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>brick:CRAC</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>entity:SSC_CCUB0007</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>entity:SSC_B1_017_MDF-2</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>B1.017 MDF-2</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>entity:SSC_B-026_MDF-Ser-1</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>B1.026 MDF/SER-1</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>B.026 MDF/SER.1</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>BF-part1</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>the BMS screen puts it in B.026 MDF/SER.1 and the ontology in B1.017 MDF-2</t>
-        </is>
-      </c>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1287,7 +1271,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_017_MDF-2</t>
+          <t>entity:SSC_B-017_MDF-2</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1324,7 +1308,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_014_VENT_PLANT</t>
+          <t>entity:SSC_B-014_Vent-Plant</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1361,7 +1345,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_014_VENT_PLANT</t>
+          <t>entity:SSC_B-014_Vent-Plant</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1398,7 +1382,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_014_VENT_PLANT</t>
+          <t>entity:SSC_B-014_Vent-Plant</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1435,7 +1419,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_014_VENT_PLANT</t>
+          <t>entity:SSC_B-014_Vent-Plant</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1450,315 +1434,287 @@
       <c r="K19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>GEFB0001</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>brick:Exhaust_Fan</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>entity:SSC_GEFB0001</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>entity:Level7_Office0367</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>the room entity entity:Level7_Office0367 carries no rdfs:label_en, so it has no readable name</t>
-        </is>
-      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>entity:SSC_B-008_Vent-Plant</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>B1.008 VENT PLANT</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>KEF-1F-0103</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>brick:Exhaust_Fan</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>entity:SSC_KEF0103</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>entity:Level7_Office0367</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>entity:SSC_01-005_Kitchen</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>1.005 KITCHEN</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>01.005 KITCHEN</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>FF-part2</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>the room entity entity:Level7_Office0367 carries no rdfs:label_en, so it has no readable name; the BMS screen puts it in 01.005 KITCHEN and the ontology in entity:Level7_Office0367</t>
-        </is>
-      </c>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>KEF0303</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>brick:Exhaust_Fan</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>entity:SSC_KEF0303</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>entity:Level7_Office0367</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>the room entity entity:Level7_Office0367 carries no rdfs:label_en, so it has no readable name</t>
-        </is>
-      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>entity:SSC_03-049_IT-Office</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>3.049 IT OFFICE</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>TEF-1F-0101</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>brick:Exhaust_Fan</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>entity:SSC_TEF0101</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>entity:Level7_Office0367</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>entity:SSC_01-028_Corridor</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>1.028 CORRIDOR</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>01.028 CORRIDOR</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>FF-part2</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K23" s="8" t="inlineStr">
-        <is>
-          <t>the room entity entity:Level7_Office0367 carries no rdfs:label_en, so it has no readable name; the BMS screen puts it in 01.028 CORRIDOR and the ontology in entity:Level7_Office0367</t>
-        </is>
-      </c>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>TEF0102</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>brick:Exhaust_Fan</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>entity:SSC_TEF0102</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>entity:Level7_Office0367</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr"/>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>the room entity entity:Level7_Office0367 carries no rdfs:label_en, so it has no readable name</t>
-        </is>
-      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>entity:SSC_01-206_Corridor</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>1.206 CORRIDOR</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>TEF0301</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>brick:Exhaust_Fan</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>entity:SSC_TEF0301</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>entity:Level7_Office0367</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr"/>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t>the room entity entity:Level7_Office0367 carries no rdfs:label_en, so it has no readable name</t>
-        </is>
-      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>entity:SSC_03-038_Server-Room</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>3.038 IT SERVER ROOM</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>TEF0302</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>brick:Exhaust_Fan</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>entity:SSC_TEF0302</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>entity:Level7_Office0367</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr"/>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>the room entity entity:Level7_Office0367 carries no rdfs:label_en, so it has no readable name</t>
-        </is>
-      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>entity:SSC_03-045_Janitors-Closet</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>3.045 JANITOR'S CLOSET</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1783,7 +1739,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_014_VENT_PLANT</t>
+          <t>entity:SSC_B-014_Vent-Plant</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -1820,7 +1776,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_014_VENT_PLANT</t>
+          <t>entity:SSC_B-014_Vent-Plant</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -1857,7 +1813,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_014_VENT_PLANT</t>
+          <t>entity:SSC_B-014_Vent-Plant</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -1894,7 +1850,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_014_VENT_PLANT</t>
+          <t>entity:SSC_B-014_Vent-Plant</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -1931,7 +1887,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_014_VENT_PLANT</t>
+          <t>entity:SSC_B-014_Vent-Plant</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -1946,118 +1902,102 @@
       <c r="K31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>DX-B-0001</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>para:DXUnit</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>entity:SSC_DXB0001</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>entity:SSC_B1_005_UPS</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>B1.005 UPS</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>entity:SSC_B-022_Ssp</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>B1.022 SSP</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>B.022 SSP</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>BF-part1</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>check</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K32" s="8" t="inlineStr">
-        <is>
-          <t>the BMS screen puts it in B.022 SSP and the ontology in B1.005 UPS; and the screen reading was itself marked as wanting a second look when it was made</t>
-        </is>
-      </c>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>DX-B-0002</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>para:DXUnit</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>entity:SSC_DXB0002</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>entity:SSC_B1_005_UPS</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>B1.005 UPS</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>entity:SSC_B-022_Ssp</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>B1.022 SSP</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>B.022 SSP</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>BF-part1</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>check</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>the BMS screen puts it in B.022 SSP and the ontology in B1.005 UPS; and the screen reading was itself marked as wanting a second look when it was made</t>
-        </is>
-      </c>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2082,7 +2022,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_005_UPS</t>
+          <t>entity:SSC_B-005_UPS</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2131,7 +2071,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_005_UPS</t>
+          <t>entity:SSC_B-005_UPS</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -2188,7 +2128,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_004_MV_SWITCH_ROOM</t>
+          <t>entity:SSC_B-004_MV-Switch-Room</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -2225,12 +2165,12 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_004_MV_SWITCH_ROOM</t>
+          <t>entity:SSC_B-033_Closet</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>B1.004 MV SWITCH ROOM</t>
+          <t>B.033 CLOSET</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -2255,7 +2195,7 @@
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>the BMS screen puts it in B.001 FM STORAGE and the ontology in B1.004 MV SWITCH ROOM</t>
+          <t>the BMS screen puts it in B.001 FM STORAGE and the ontology in B.033 CLOSET</t>
         </is>
       </c>
     </row>
@@ -2282,12 +2222,12 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_019_FM_STORAGE</t>
+          <t>entity:SSC_B-003_Transformer</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>B1.019 FM STORAGE</t>
+          <t>B1.003 TRANSFORMER</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -2312,7 +2252,7 @@
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>the BMS screen puts it in B.006 SERVICE AREA and the ontology in B1.019 FM STORAGE</t>
+          <t>the BMS screen puts it in B.006 SERVICE AREA and the ontology in B1.003 TRANSFORMER</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2279,12 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_019_FM_STORAGE</t>
+          <t>entity:SSC_B-003_Transformer</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>B1.019 FM STORAGE</t>
+          <t>B1.003 TRANSFORMER</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -2369,66 +2309,58 @@
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>the BMS screen puts it in B.008 VENT PLANT and the ontology in B1.019 FM STORAGE</t>
+          <t>the BMS screen puts it in B.008 VENT PLANT and the ontology in B1.003 TRANSFORMER</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>DX-B-0009</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>para:DXUnit</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>entity:SSC_DXB0009</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>entity:SSC_B1_020_FM_STORAGE</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>B1.020 FM STORAGE</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>entity:SSC_B-002_HV-Room</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>B1.002 HV</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>B.002 HV ROOM</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>BF-part2</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K40" s="8" t="inlineStr">
-        <is>
-          <t>the BMS screen puts it in B.002 HV ROOM and the ontology in B1.020 FM STORAGE</t>
-        </is>
-      </c>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -2453,12 +2385,12 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_021_FM_STORAGE</t>
+          <t>entity:SSC_B-002_HV-Room</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>B1.021 FM STORAGE</t>
+          <t>B1.002 HV</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -2483,7 +2415,7 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>the BMS screen puts it in B.033 CLOSET and the ontology in B1.021 FM STORAGE; and the screen reading was itself marked as wanting a second look when it was made</t>
+          <t>the BMS screen puts it in B.033 CLOSET and the ontology in B1.002 HV; and the screen reading was itself marked as wanting a second look when it was made</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2442,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>entity:SSC_B1_012_GENERATOR</t>
+          <t>entity:SSC_B-012_Generator</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -7263,21 +7195,21 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>brick:CRAC</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>2</v>
+      <c r="D12" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7299,21 +7231,21 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>brick:Exhaust_Fan</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="D14" s="9" t="n">
-        <v>7</v>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -7349,7 +7281,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
